--- a/translate_paq_and_qqp/dataset_paq_traducido.xlsx
+++ b/translate_paq_and_qqp/dataset_paq_traducido.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2968,1181 +2968,6 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>20631</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>when did the for-profit university of phoenix open</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>John Sperling John Glen Sperling (January 9, 1921 – August 22, 2014) was an American businessman who is credited with having led the contemporary for-profit education movement in the United States. The fortune he amassed was based on his founding of the for-profit University of Phoenix for working adults in 1976, which is now part of the publicly traded Apollo Group. For ventures ranging from pet cloning to green energy, he has widely been described as an "eccentric" self-made man by the "Washington Post" and other media. Sperling was born to a poor sharecropper family in the Missouri Ozarks. His</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>¿Cuándo abrió la universidad con fines de lucro de Phoenix</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>John Sperling John Glen Sperling (9 de enero de 1921 – 22 de agosto de 2014) fue un hombre de negocios estadounidense que se le atribuye haber dirigido el movimiento educativo contemporáneo con fines de lucro en los Estados Unidos. La fortuna que acumuló se basó en su fundación de la Universidad de Phoenix con fines de lucro para adultos trabajadores en 1976, que ahora forma parte del grupo Apollo. Para empresas que van desde la clonación de mascotas a la energía verde, ha sido descrito ampliamente como un hombre auto-hecho "eccéntrico" por el "Washington Post" y otros medios. Sperling nació de una familia pobre de aparceros en los Ozarks de Missouri.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>20632</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>how does euclid prove every finite list has a property</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Euclid's theorem This proves that for every finite list of prime numbers there is a prime number not on the list, and therefore there must be infinitely many prime numbers. Euclid is often erroneously reported to have proved this result by contradiction, beginning with the assumption that the finite set initially considered contains all prime numbers, or that it contains precisely the "n" smallest primes, rather than any arbitrary finite set of primes. Instead of a proof by contradiction, Euclid's proof shows that every finite list has a particular property. A contradiction is not inferred, but none of the items on the</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>¿Cómo prueba Euclid cada lista finita tiene una propiedad</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Esto demuestra que para cada lista finita de números primos no hay un número primo en la lista, y por lo tanto debe haber infinitamente muchos números primos. Euclides es a menudo erróneamente reportado que ha demostrado este resultado por contradicción, comenzando con la suposición de que el conjunto finito inicialmente considerado contiene todos los números primos, o que contiene precisamente los primos más pequeños "n", en lugar de cualquier conjunto finito arbitrario de primos. En lugar de una prueba por contradicción, la prueba de Euclides muestra que cada lista finita tiene una propiedad particular. Una contradicción no se infiere, pero ninguno de los elementos en el</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>20633</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>who played electric guitar on songs from the wood</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Songs from the Wood the cultural and historical significance of making that commitment to English residency." Being the first Jethro Tull album to feature keyboardist David Palmer as an official band member, their music gained complexity and variety, with more instruments being played and a sound that derives from Palmer's classical leanings and the strong presence of Martin Barre's electric guitar. Both Palmer and Barre are credited for contributing material to the album. The album highlights the band at its most playful and due to its lush production and more noticeable use of keyboards is perhaps one of the band's most obviously progressive rock-oriented</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>que tocaba la guitarra eléctrica en las canciones de la madera</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Al ser el primer álbum de Jethro Tull en presentar al teclista David Palmer como miembro oficial de la banda, su música ganó complejidad y variedad, con más instrumentos siendo tocados y un sonido que deriva de las inclinaciones clásicas de Palmer y la fuerte presencia de la guitarra eléctrica de Martin Barre. Tanto Palmer como Barre son acreditados por aportar material al álbum. El álbum destaca a la banda en su más sonoro y debido a su exuberante producción y uso más notable de los teclados es tal vez uno de los más obviamente progresivos del grupo orientado al rock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>20634</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>who occupied the gulf coast of the atlantic</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Pierre Le Moyne d'Iberville the summer of 1697. Soon after his departure, the English arrived in Newfoundland with 2,000 troops and restored their position. Hostilities ended with the Treaty of Ryswick in September 1697. In 1682, René-Robert Cavelier, Sieur de La Salle was the first European to travel from the Great Lakes down the Mississippi River to the Gulf of Mexico. The French began dreaming of building a great empire by linking the Saint Lawrence and Mississippi basins, thereby bottling up the English on the Atlantic coast. This presented diplomatic problems; because the Gulf coast was claimed, but not occupied, by Spain. Pontchartrain, the</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>que ocupó la costa del golfo del Atlántico</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Pierre Le Moyne d'Iberville el verano de 1697. Poco después de su partida, los ingleses llegaron a Terranova con 2.000 tropas y restauraron su posición. Hostilidades terminaron con el Tratado de Ryswick en septiembre de 1697. En 1682, René-Robert Cavelier, Sieur de La Salle fue el primer europeo en viajar desde los Grandes Lagos por el río Mississippi hasta el Golfo de México. Los franceses comenzaron a soñar con construir un gran imperio uniendo las cuencas de San Lorenzo y Mississippi, embotellando así a los ingleses en la costa atlántica. Esto presentó problemas diplomáticos; porque la costa del Golfo fue reclamada, pero no ocupada, por España. Pontchartrain, el</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>20635</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>when did john dewey write about teachers</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>John Dewey must aspire to share what she knows with others in her learning community. The best indicator of teacher quality, according to Dewey, is the ability to watch and respond to the movement of the mind with keen awareness of the signs and quality of the responses he or her students exhibit with regard to the subject-matter presented (Dewey, APT, 2010; Dewey, 1904). As Dewey notes, "I have often been asked how it was that some teachers who have never studied the art of teaching are still extraordinarily good teachers. The explanation is simple. They have a quick, sure and unflagging</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Cuando John Dewey escribió sobre los maestros</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>John Dewey debe aspirar a compartir lo que sabe con los demás en su comunidad de aprendizaje. El mejor indicador de la calidad del maestro, según Dewey, es la capacidad de observar y responder al movimiento de la mente con gran conciencia de los signos y la calidad de las respuestas que exhiben sus alumnos con respecto a la materia presentada (Dewey, APT, 2010; Dewey, 1904). Como señala Dewey, "A menudo se me ha preguntado cómo fue que algunos profesores que nunca han estudiado el arte de la enseñanza siguen siendo maestros extraordinariamente buenos. La explicación es simple. Tienen un rápido, seguro y sin trabas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>20636</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>who said that benjamin britten was a phenomenal father figure</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Benjamin Britten to imitate". Nevertheless, after his death Britten was lauded by the younger generation of English composers to whom, in the words of Oliver Knussen, he became "a phenomenal father-figure". Brett believes that he affected every subsequent British composer to some extent: "He is a key figure in the growth of British musical culture in the second half of the 20th century, and his effect on everything from opera to the revitalization of music education is hard to overestimate." Whittall believes that one reason for Britten's enduring popularity is the "progressive conservatism" of his music. He generally avoided the avant garde,</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>que dijo que benjamin britten era una figura padre fenomenal</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Sin embargo, después de su muerte Britten fue elogiado por la generación más joven de compositores ingleses a quienes, en palabras de Oliver Knussen, se convirtió en "una fenomenal figura paterna". Brett cree que afectó a todos los compositores británicos posteriores hasta cierto punto: "Él es una figura clave en el crecimiento de la cultura musical británica en la segunda mitad del siglo XX, y su efecto en todo, desde la ópera hasta la revitalización de la educación musical es difícil de sobreestimar". Whittall cree que una razón de la popularidad duradera de Britten es el "conservadurismo progresista" de su música. Generalmente evitó la vanguardia,</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>20637</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>how many times did erik van dillen win the junior world tennis championship</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Erik van Dillen Erik van Dillen (born February 21, 1951) is an American former professional tennis player who played over 25 major Grand Slam Championships: Australian Open, French Open, Wimbledon and U.S. Open. Born in San Mateo, California, van Dillen first played tennis aged six years old. During his junior tennis career he won both the singles and doubles competitions at the USTA Boys 16 &amp; 18 National Championships in Kalamazoo, Michigan, as well as winning other national titles in the 12- and 14-year-old divisions. In total he won 12 U.S. Junior Titles and is the only player ever to</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>cuántas veces Erik van Dillen ganó el campeonato mundial de tenis junior</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Erik van Dillen Erik van Dillen (nacido el 21 de febrero de 1951) es un ex jugador de tenis profesional estadounidense que jugó más de 25 grandes campeonatos de Grand Slam: Australian Open, French Open, Wimbledon y U.S. Open. Nacido en San Mateo, California, van Dillen jugó tenis por primera vez a partir de seis años de edad. Durante su carrera de tenis junior ganó tanto los singles como las competiciones de dobles en el USTA Boys 16 &amp; 18 National Championships en Kalamazoo, Michigan, así como ganar otros títulos nacionales en las divisiones de 12 y 14 años de edad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>20638</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>who funded the restoration of i take this woman in 1931</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>I Take This Woman (1931 film) hurt. Kay rushes to Tom's side, and the two reconcile and decide to return to the ranch. This film apparently became an "orphan film" when the rights reverted to author Mary Roberts Rinehart. The original 35mm negative and all supporting material was shipped back to her, but she had no interest in (or appropriate storage for) the material. A single surviving nitrate print from the UCLA Film and Television Archive became the basis for a restoration, funded by the Louis B. Mayer Foundation. The restored print was screened in March 2017 at the Festival of Preservation at UCLA. I Take</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>que financió la restauración de esta mujer en 1931</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Me llevo a esta mujer (1931 película) herido. Kay se precipita al lado de Tom, y los dos se reconcilian y deciden volver al rancho. Esta película aparentemente se convirtió en una "película huérfana" cuando los derechos volvieron a la autora Mary Roberts Rinehart. El original 35mm negativo y todo el material de apoyo fue enviado de vuelta a ella, pero ella no tenía interés en (o almacenamiento apropiado para) el material. Una sola impresión de nitrato sobreviviente del Archivo de Cine y Televisión de la UCLA se convirtió en la base para una restauración, financiada por la Fundación Louis B. Mayer. La impresión restaurada fue proyectada en marzo de 2017 en el Festival de Preservación de la UCLA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>20639</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>in 1846 new mexico became part of what country</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>months and return to lower elevations in the winter. The first known occupation of the Pecos Wilderness began in 1598 with the colonization by Spain. During the next 200 years they would push into the fertile lands that flanked the Sangre de Cristo Mountain range. New Mexico was annexed to the United States following the Mexican war of 1846. In 1875 mineral prospecting began. George Beatty was an early pioneer who built a cabin at the junction of the Pecos river and the Rito del Padre. Beatty flats are named after him. The high altitude of the Pecos provides a</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>en 1846 nuevo México se convirtió en parte de qué país</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>La primera ocupación conocida de los Pecos Wilderness comenzó en 1598 con la colonización por España. Durante los próximos 200 años se introducirían en las fértiles tierras que flanqueaban la Cordillera Sangre de Cristo. Nuevo México se anexionó a los Estados Unidos después de la guerra mexicana de 1846. En 1875 comenzó la prospección minera. George Beatty fue un pionero temprano que construyó una cabaña en el cruce del río Pecos y el Rito del Padre. Los pisos Beatty llevan su nombre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>20640</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>who does elaine may play in luv movie</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Luv (film) Falk), an old friend from fifteen years ago. Harry doesn't really recognize him at first but there appears to be a contrast between the two of them with Milt boasting of how well he is doing in life while Harry tries to listen. Milt takes Harry to his house to meet Ellen Manville (Elaine May), Milt's long-suffering wife. She is complaining that their sex life is non-existent but Milt has a secret lover in the form of beautiful blonde Linda (Nina Wayne). Milt convinces a barely-there Harry to make a go of things with Ellen so that she is not</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>que hace Elaine puede jugar en la película de luv</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Luv (film) Falk), un viejo amigo de hace quince años. Harry realmente no lo reconoce al principio, pero parece haber un contraste entre los dos de ellos con Milt alardeando de lo bien que está haciendo en la vida mientras Harry trata de escuchar. Milt lleva a Harry a su casa para conocer a Ellen Manville (Elaine May), la esposa de Milt que sufre mucho tiempo. Ella se queja de que su vida sexual es inexistente, pero Milt tiene un amante secreto en forma de hermosa rubia Linda (Nina Wayne). Milt convence a un Harry apenas-allí para hacer un ir de las cosas con Ellen para que ella no es</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>20641</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>when was the albert v bryan building named</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Albert V. Bryan United States Courthouse The Albert V. Bryan United States Courthouse is a United States courthouse of the United States District Court for the Eastern District of Virginia. It is located at 401 Courthouse Square (2200 Jamieson Avenue) in Alexandria, Va., and was built in the early 1990s. It was named in honor of U.S. District Court judge Albert V. Bryan on June 26, 1995, through Congressional legislation sponsored by U.S. Senator John Warner of Virginia. From the mid-1980s until 1995, the name was applied to the 1932 federal courthouse at 200 South Washington Street that is now</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>cuando se llamaba el edificio Albert v Brian</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Albert V. Bryan Tribunal de los Estados Unidos El Tribunal de los Estados Unidos Albert V. Bryan es un tribunal de los Estados Unidos del Tribunal de Distrito de los Estados Unidos para el Distrito Oriental de Virginia. Se encuentra en 401 Courthouse Square (2200 Jamieson Avenue) en Alejandría, Va., y fue construido a principios de los años 90. Fue nombrado en honor del juez del Tribunal de Distrito de los Estados Unidos Albert V. Bryan el 26 de junio de 1995, a través de la legislación del Congreso patrocinada por el senador estadounidense John Warner de Virginia. Desde mediados de la década de 1980 hasta 1995, el nombre se aplicó al tribunal federal de 1932 en 200 South Washington Street que ahora es</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>20642</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>how long did jill mcdonald work at british airways</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Jill McDonald (businesswoman) Palmolive. In 1990, she joined British Airways as a brand manager, and worked there for 16 years, rising to head of global marketing, before joining McDonald's in 2006. In 2006, she joined McDonald's as chief marketing officer for the UK and northern Europe, and in 2010, was promoted to CEO of McDonald's UK and president of North West Europe. In May 2015, McDonald replaced Matt Davies (who left to join Tesco), as CEO of Halfords, on a basic salary of £500,000 plus bonuses. As of May 2017, she is due to take over as head of Marks &amp; Spencer's non-food</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>¿Cuánto tiempo trabajó Jill Mcdonald en las vías respiratorias británicas?</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Jill McDonald (empresaria) Palmolive. En 1990, se unió a British Airways como gerente de marca, y trabajó allí durante 16 años, subiendo a la cabeza de marketing global, antes de unirse a McDonald's en 2006. En 2006, se unió a McDonald's como directora de marketing para el Reino Unido y el norte de Europa, y en 2010, fue ascendido a CEO de McDonald's UK y presidente de North West Europe. En mayo de 2015, McDonald reemplazó a Matt Davies (que dejó para unirse a Tesco), como CEO de Halfords, con un salario básico de 500.000 libras más bonificaciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>20643</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>when did ken hackett go to catholic relief services</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ken Hackett Kenneth Francis Hackett (born January 27, 1947) was the United States Ambassador to the Holy See from August 2013 until January 2017. He was previously president of Catholic Relief Services (CRS). Hackett attended Boston College, graduating in 1968. He then joined the Peace Corps and served in Ghana. Afterwards, he joined Catholic Relief Services (CRS), serving in Africa and Asia. He was named the president of CRS, retiring in 2011. He was nominated to the post by President Barack Obama in June 2013 and confirmed by the Senate on August 1, 2013. He presented his Letters of Credence</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>¿Cuándo fue Ken Hackett a los servicios católicos de socorro</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Ken Hackett Kenneth Francis Hackett (nacido el 27 de enero de 1947) fue el embajador de los Estados Unidos ante la Santa Sede desde agosto de 2013 hasta enero de 2017. Anteriormente fue presidente de Catholic Relief Services (CRS). Hackett asistió al Boston College, se graduó en 1968. Luego se unió al Cuerpo de Paz y sirvió en Ghana. Posteriormente, se unió a Catholic Relief Services (CRS), sirviendo en África y Asia. Fue nombrado presidente de CRS, retirándose en 2011. Fue nominado al cargo por el presidente Barack Obama en junio de 2013 y confirmado por el Senado el 1 de agosto de 2013.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>20644</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>which planet in the solar system has gained neechbhanga</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>is formed by Capricorn, which is a bad sign owned by Saturn, a natural malefic, and the 9th house receives the combined aspect of Saturn, Mars, Venus and Rahu, denoting a miserable bhagya, but an exalted Moon aspects Saturn and Mars, Mars has gained "neechbhanga", and its dipositor, the exalted Moon, also occupies the Lagna-kendra which situation has given rise to Neechabhanga Raja yoga. In the case of Barack Obama born in Capricorn lagna occupied by Jupiter and Saturn, Jupiter gains "neechabhanga" and causes Neechabhanga Raja yoga; because the debilitated Jupiter occupying Capricorn, its sign of debilitation, is in the</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>que planeta en el sistema solar ha ganado neechbhanga</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>está formada por Capricornio, que es una mala señal propiedad de Saturno, un maléfico natural, y la 9a casa recibe el aspecto combinado de Saturno, Marte, Venus y Rahu, que denota un miserable bhagya, pero un exaltado aspecto lunar Saturno y Marte, Marte ha ganado "neechbhanga", y su dipositor, la exaltada Luna, también ocupa el Lagna-kendra, cuya situación ha dado lugar a Neechabhanga Raja yoga. En el caso de Barack Obama nacido en Capricornio lagna ocupado por Júpiter y Saturno, Júpiter gana "neechabhanga" y causa Neechabhanga Raja yoga; porque el Júpiter debilitado ocupando Capricornio, su signo de debilidad, está en el</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>20645</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>when did alyssa healy play her first international match</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Alyssa Healy any wicket-keeper in the Women's National Cricket League. Following the injury to Australian captain and wicket-keeper Jodie Fields, Healy was given her international debut in the 2010 Rose Bowl series against New Zealand. She played in the first five One Day Internationals (ODIs) and five Twenty20 (T20) internationals, but was dropped for the last three ODIs during the New Zealand leg of the series. Healy played in every match of the 2010 World Twenty20 as Australia won the tournament after an unbeaten campaign. Healy is the daughter of Greg, who was a member of the Queensland squad, while Greg's younger</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Cuando Alyssa Healy jugó su primer partido internacional</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Alyssa Healy cualquier wicket-keeper en la Liga Nacional de Cricket Femenina. Después de la lesión a la capitana australiana y wicket-keeper Jodie Fields, Healy fue dado su debut internacional en la serie de 2010 Rose Bowl contra Nueva Zelanda. Ella jugó en los primeros cinco internacionales de un día (ODI) y cinco internacionales de T20, pero fue abandonado para los últimos tres ODIs durante la etapa de Nueva Zelanda de la serie. Healy jugó en cada partido de la 2020 Mundial 2010 como Australia ganó el torneo después de una campaña invicta. Healy es la hija de Greg, que era miembro del equipo de Queensland, mientras Greg's más joven</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>20646</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>which is the second stage of the international physics olympiad</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>and "Best Solution (Theory)" are awarded in the OCSC, with cash prizes. 2.All INPhO qualifiers get gold medals, books and certificates 3.Those sitting for NSEP may get National Top 1%, State Top 1% or Centre Top 10% certificates, the first accompanied with book prizes 4. The selected Indian team members get 8000 Rupees in form of books and cash. Indian National Physics Olympiad The Indian National Physics Olympiad (INPhO in short) is the second stage of the five-stage Olympiad programme for Physics in India. It ultimately leads to the selection in the International Physics Olympiad. INPhO is conducted on the</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>que es la segunda etapa de la física internacional olympiad</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>y "Mejor Solución (Teoría)" se otorgan en la OCSC, con premios en efectivo. 2.Todos los calificadores INPHO obtienen medallas de oro, libros y certificados 3.Aquellos que se sientan para la NSEP pueden obtener los certificados Nacional Top 1%, Estatal Top 1% o Centro Top 10%, el primero acompañado con premios de libro 4. Los miembros seleccionados del equipo indio obtienen 8000 Rupias en forma de libros y efectivo. India Nacional Física Olimpiada La Olimpiada Nacional de Física de la India (INPhO en resumen) es la segunda etapa del programa de cinco etapas de la Olimpiada de Física en la India.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>20647</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>where did the spatafore family go in chasing it</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Chasing It son, Vito Jr., who has become antisocial following his father's murder. Marie also requests $100,000 to move her family to Maine to start over. Tony resists and suggests that Phil, who killed Vito, should get involved. Phil agrees to talk to Vito's son. Both men each talk to Vito Jr. to try to make him stop his delinquency, but their attempts fail. Neither of them are willing to fund the Spatafore family's move to Maine. After Vito Jr. is expelled for defecating in the school shower, Tony changes his mind and says he will pay for the Spatafores' relocation. He</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>¿Dónde fue la familia Spatafore a perseguirlo?</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>El hijo de Chasing It, Vito Jr., que se ha vuelto antisocial después del asesinato de su padre. Marie también pide $100.000 para trasladar a su familia a Maine para empezar de nuevo. Tony se resiste y sugiere que Phil, quien mató a Vito, debería involucrarse. Phil acepta hablar con el hijo de Vito. Ambos hombres hablan cada uno con Vito Jr. para tratar de hacerle detener su delincuencia, pero sus intentos fracasan. Ninguno de ellos está dispuesto a financiar la mudanza de la familia Spatafore a Maine. Después de Vito Jr. es expulsado por defecar en la ducha de la escuela, Tony cambia de opinión y dice que pagará por la reubicación de los Spatafores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>20648</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>where is chinese christian school located in california</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Chinese Christian Schools Chinese Christian Schools, also known as "CCS" (Chinese Traditional: 華人基督教學校, Simplified: 华人基督教学校, Pinyin: "Huárén Jīdūjiào Xuéxiào"), includes elementary education. CCS is located in Alameda, California. The majority of the student population is Chinese or of other Asian ethnicity, however students of other ethnic groups are not uncommon. As CCS is a private school, all students are required to pay a nominal tuition fee. The school describes itself as "an educational ministry that is college preparatory in academics, Christian in philosophy, and Chinese in culture." The motto of Chinese Christian High School is "Transforming Lives for the Glory</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>donde está la escuela cristiana china ubicada en California</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Las escuelas cristianas chinas Las escuelas cristianas chinas, también conocidas como "CCS" (Tradicional Chino: , Simplificado: , Pinyin: "Huárén Jīdūjiào Xuéxiào"), incluyen la educación primaria. CCS se encuentra en Alameda, California. La mayoría de la población estudiantil es china o de otra etnia asiática, sin embargo los estudiantes de otros grupos étnicos no son infrecuentes. Como CCS es una escuela privada, todos los estudiantes están obligados a pagar una cuota nominal de matrícula. La escuela se describe como "un ministerio educativo que es preparatorio universitario en los académicos, cristiano en filosofía, y chino en la cultura".</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>20649</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>how many wickets did somerset lose in the 2005 t20 final</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2005 Twenty20 Cup Final to bat first. Before the start of play, the game had been reduced to 16 overs-a-side. Lancashire scored 114 runs in their batting overs, but lost regular wickets. Their innings was held together by Australian batsman Stuart Law, who top-scored for the county, accruing 59 runs. In their response, Somerset only lost three wickets, and during an innings dominated by the batting of Graeme Smith, reached their winning target with 11 balls remaining. Rain delayed the start of the match by an hour, and shortened it to a 16 over-per-side contest. Lancashire captain Mark Chilton opted to bat first having</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>cuántos wickets perdió somerset en el 2005 t20 final</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2005 Twenty20 Cup Final para batear primero. Antes del inicio del juego, el juego había sido reducido a 16 overs-a-side. Lancashire anotó 114 carreras en sus bateo sobres, pero perdió wickets regulares. Sus entradas fueron mantenidas juntas por el bateador australiano Stuart Law, que obtuvo el mejor puntaje para el condado, acumulando 59 carreras. En su respuesta, Somerset sólo perdió tres wickets, y durante una entradas dominadas por el bateo de Graeme Smith, alcanzó su objetivo ganador con 11 bolas restantes. Lluvia retrasó el inicio del partido por una hora, y lo acortó a un 16 sobre-por-side concurso. Lancashire capitán Mark Chilton optó por batear primero teniendo</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>20650</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>who had a christmas no.1 in 2000 with 'can we fix it'</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2000 in British music charts they were all beaten by a special novelty release that captured the hearts of many fans across the festive season. "Can We Fix It?" by Bob the Builder became 2000's Christmas No. 1 single and quickly became the biggest selling single of the year. He had become very popular through his successful television series and this was the start of a very short lived, but moderately successful singing career. He destroyed the run of consecutive No. 1 singles of Westlife, ending it at 7, keeping "What Makes A Man" at #2. Reigning supreme at the top of the albums chart</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>que tuvo una Navidad número 1 en 2000 con "podemos arreglarlo"</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2000 en listas de música británicas fueron derrotados por un lanzamiento de novedad especial que capturó los corazones de muchos fans a lo largo de la temporada festiva. "¿Podemos arreglarlo?" por Bob the Builder se convirtió en el single de Navidad número 1 del 2000 y rápidamente se convirtió en el single más vendido del año. Se había hecho muy popular a través de su exitosa serie de televisión y este fue el comienzo de una carrera de canto muy corta, pero moderadamente exitosa. Destruyó la carrera de sencillos consecutivos número 1 de Westlife, terminando en 7, manteniendo "What Makes A Man" en el #2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>20651</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>who created the code of canon law that governs the clergy</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Bishop in the Catholic Church amounts to presiding at meetings and overseeing a diocese which has no bishop. In Eastern Catholicism a metropolitan may also be the head of an autocephalous, "sui juris", or autonomous church when the number of adherents of that tradition is small. In the Latin Church, metropolitans are always archbishops; in many Eastern churches, the title is "Metropolitan," with some of these churches using "archbishop" as a separate office. Since the publication of the new Code of Canon Law in 1983 by Pope John Paul II, all members of the Catholic clergy are forbidden to hold public office without the express</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>que creó el código de derecho canónico que gobierna el clero</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Obispo en la Iglesia Católica equivale a presidir reuniones y supervisar una diócesis que no tiene obispo. En el catolicismo oriental un metropolitano también puede ser el jefe de un autocéfalo, "sui juris", o iglesia autónoma cuando el número de adeptos de esa tradición es pequeño. En la Iglesia Latina, los metropolitanos son siempre arzobispos; en muchas iglesias orientales, el título es "Metropolitano", con algunas de estas iglesias usando "archibispo" como una oficina separada. Desde la publicación del nuevo Código de Derecho Canónico en 1983 por el Papa Juan Pablo II, todos los miembros del clero católico están prohibidos para ocupar cargos públicos sin el expreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>20652</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>in which shakespeare play does jessica elope with her father</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Jessica (The Merchant of Venice) Jessica is the daughter of Shylock, a Jewish moneylender, in William Shakespeare's "The Merchant of Venice" (). In the play, she elopes with Lorenzo, a pennyless Christian, and a chest of her father's money, eventually ending up in Portia and Bassanio's household. In the play's dramatic structure, Jessica is a minor but pivotal role. Her actions motivate Shylock's vengeful insistence on his "pound of flesh" from Antonio; her relationships with Lorenzo and Shylock serves as a mirror and contrast to Portia's with Bassanio and with her father; her conversion to Christianity is the end of</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>en la que Shakespeare juega hace jessica fugarse con su padre</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Jessica (El mercader de Venecia) Jessica es la hija de Shylock, un prestamista judío, en el "El mercader de Venecia" de William Shakespeare (). En la obra, ella se fuga con Lorenzo, un cristiano sin dinero, y un cofre del dinero de su padre, terminando finalmente en la casa de Portia y Bassanio. En la estructura dramática de la obra, Jessica es un papel menor pero fundamental. Sus acciones motivan la vengativa insistencia de Shylock en su "libra de carne" de Antonio; sus relaciones con Lorenzo y Shylock sirve como un espejo y contrastan con Portia con Bassanio y con su padre; su conversión al cristianismo es el final de la</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>20653</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>what is the most popular type of beer in norway</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>which is illegal) pastime. Examples can be found in Oslo at Oslo Mikrobryggeri, Scandinavia's first microbrewery and brewpub, Molo Brew in Ålesund, and Lervig in Stavanger. As with most countries in Europe and America, the most popular style of beer in Norway is pilsner-style pale lager. According to the Norwegian brewers' association, most beer brewed in Norway is pale lager. Until recently, this was the only style of beer to be had, except at Christmas time, when Christmas beers become available. These are dark malt beers traditionally brewed for the holiday season. Today, the craft beer market has continued to</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>cuál es el tipo de cerveza más popular en Noruega</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>, que es ilegal) pasatiempo. Ejemplos se pueden encontrar en Oslo en Oslo Mikrobryggeri, la primera microcervecería y cervecería de Escandinavia, Molo Brew en Ålesund, y Lervig en Stavanger. Al igual que con la mayoría de los países de Europa y América, el estilo más popular de cerveza en Noruega es cerveza pilsner estilo cerveza pálida. Según la asociación de cerveceros noruegos, la mayoría de cerveza elaborada en Noruega es cerveza pálida. Hasta hace poco, este era el único estilo de cerveza que se tenía, excepto en Navidad, cuando las cervezas de Navidad están disponibles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>20654</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>when was the first virtual fixture invented</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Virtual fixture A virtual fixture is an overlay of augmented sensory information upon a user's perception of a real environment in order to improve human performance in both direct and remotely manipulated tasks. Developed in the early 1990s by Louis Rosenberg at the U.S. Air Force Research Laboratory (AFRL), Virtual Fixtures was a pioneering platform in virtual reality and augmented reality technologies. Virtual Fixtures was first developed by Louis Rosenberg in 1992 at the USAF Armstrong Labs, resulting in the first immersive augmented reality system ever built. Because 3D graphics were too slow in the early 1990s to present a</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>cuando fue el primer accesorio virtual inventado</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Fijación virtual Un dispositivo virtual es una superposición de información sensorial aumentada sobre la percepción del usuario de un entorno real para mejorar el rendimiento humano en tareas tanto directas como manipuladas remotamente. Desarrollado a principios de la década de 1990 por Louis Rosenberg en el Laboratorio de Investigación de la Fuerza Aérea de EE.UU. (AFRL), Virtual Fixtures fue una plataforma pionera en realidad virtual y tecnologías de realidad aumentada. Virtual Fixtures fue desarrollado por primera vez por Louis Rosenberg en 1992 en los Laboratorios Armstrong USAF, resultando en el primer sistema de realidad aumentada inmersiva jamás construido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>20655</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>how long is the road to mount scopus</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Mount Scopus road, a mile and a half long, passing through the Arab neighbourhood of Sheikh Jarrah. Arab sniper fire on vehicles moving along the access route became a regular occurrence, and road mines were laid. When food and supplies at the hospital begun to dwindle, a large convoy carrying doctors and supplies set out for the besieged hospital, leading to an attack that became known as the Hadassah medical convoy massacre. Seventy-eight Jewish doctors, nurses, students, patients, faculty members and Haganah fighters, and one British soldier were killed in the attack. After the ceasefire agreement of November 30, 1948, which established</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>¿Cuánto tiempo es el camino para montar el scopus</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>La carretera del Monte Scopus, de una milla y media de largo, que pasa por el barrio árabe del Jeque Jarrah. Los disparos de francotiradores árabes contra vehículos que se desplazaban por la ruta de acceso se hicieron frecuentes y se colocaron minas en las carreteras. Cuando comenzaron a disminuir los alimentos y suministros en el hospital, un gran convoy que transportaba médicos y suministros partió hacia el hospital sitiado, lo que dio lugar a un ataque conocido como la masacre del convoy médico de Hadassah. Setenta y ocho médicos judíos, enfermeras, estudiantes, pacientes, miembros de la facultad y combatientes de Haganah, y un soldado británico murieron en el ataque.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>20656</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>who sings if ever i could love darrell brown</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Darrell Brown (musician) hit single for Josh Turner, "Why Don't We Just Dance", was Number #1 on the "Billboard" Country Charts for four weeks in a row. The longest running number 1 single of Josh Turner's career and Turner's first Number 1 single on the Canadian Country Charts. "Why Don't We Just Dance" was the Most Played Country Single of The Year in 2010 according to Mediabase. John Mayer and Keith Urban recently performed one of Darrell's songs "If Ever I Could Love” on a newly filmed Country Music Television (CMT) Crossroads Television Special for CMT and Brown's songs "Good Friend and a</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>que canta si alguna vez pudiera amar a Darrell Brown</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>"Why Don't We Just Dance", fue el número #1 en el "Billboard" Country Charts durante cuatro semanas consecutivas. El single número 1 más largo de la carrera de Josh Turner y el primer single número 1 de Turner en el Canadian Country Charts. "Why Don't We Just Dance" fue el Single Country más jugado del año en 2010 según Mediabase. John Mayer y Keith Urban interpretaron recientemente una de las canciones de Darrell "If Ever I Could Love" en una nueva película Country Music Television (CMT) Crossroads Television Especial para las canciones de CMT y Brown "Good Friend and a</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>20657</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>on what date did qatar airways launch its first commercial flight</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>4 Airbus A321 aircraft worth $1.9bn. On October 12, 2009, the company completed the world's first commercial passenger flight powered by a fuel made from natural gas, Also in 2009, Qatar Airways launched its first scheduled flights to Australia with Melbourne being the first city served; routes to Chengdu, Hangzhou, Phnom Penh and Clark International Airport in the Philippines were launched during as well. Tokyo-Narita was first served by the carrier in . On May 18, 2010, the airline put its first Boeing 777F (A7-BFA) into service, with a flight from Doha to Amsterdam. The aircraft had been delivered on</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>¿En qué fecha las vías aéreas de qatar lanzaron su primer vuelo comercial?</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>El 12 de octubre de 2009, la compañía completó el primer vuelo comercial de pasajeros del mundo propulsado por un combustible hecho a gas natural, También en 2009, Qatar Airways lanzó sus primeros vuelos regulares a Australia con Melbourne siendo la primera ciudad servida; rutas a Chengdu, Hangzhou, Phnom Penh y Clark Aeropuerto Internacional en Filipinas también se lanzaron durante. Tokio-Narita fue servido por primera vez por el transportista en . El 18 de mayo de 2010, la aerolínea puso en servicio su primer Boeing 777F (A7-BFA), con un vuelo de Doha a Amsterdam. El avión había sido entregado en</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>20658</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>when was bain capital acquired by hoechst</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>subsequently with the Behring Diagnostics division of Hoechst AG in 1997. Aventis, the successor of Hoechst, acquired 52% of the combined company. In 1999, the company reported $1.3 billion of revenue and completed a $1.25 billion leveraged recapitalization that resulted in a payout to shareholders. The dividend, taken together with other previous shareholder dividends resulted in an eightfold return on investment to Bain Capital and Goldman Sachs. Revenues declined from 1999 through 2002 and despite attempts to cut costs through layoffs the company entered into bankruptcy in 2002. Following its restructuring, Dade Behring emerged from Bankruptcy in 2003 and continued</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>cuando el capital del bain fue adquirido por Hoechst</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Posteriormente, con la división Behring Diagnostics de Hoechst AG en 1997. Aventis, el sucesor de Hoechst, adquirió el 52% de la compañía combinada. En 1999, la compañía reportó $1.3 mil millones de ingresos y completó una recapitalización apalancada de $1.250 millones que resultó en un pago a los accionistas. El dividendo, tomado junto con otros dividendos anteriores de los accionistas resultó en un retorno ocho veces superior a la inversión en Bain Capital y Goldman Sachs. Los ingresos disminuyeron de 1999 a 2002 y a pesar de los intentos de reducir los costos mediante despidos la empresa entró en quiebra en 2002.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>20659</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>what was the smell of in the dreaded batter pudding hurler</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>The Dreaded Batter Pudding Hurler (of Bexhill-on-Sea) the phone rings; it's Clement Attlee, complaining that someone's just thrown a batter pudding at him. Seagoon encounters Moriarty dressed as a chef and pulling a portable gas stove from which comes the smell of batter pudding, but dismisses him as irrelevant to the investigation. It is finally discovered that the hurler is in Africa, and Seagoon and Bluebottle travel there on a ship disguised as a train, done up like a boat and painted to appear like a tram. After the ship is destroyed by a mine which Eccles considers not to be a problem because "it's one of</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>lo que era el olor de en el temido lanzador de pudín de bateo</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>El Dreaded Batter Pudding Hurler (de Bexhill-on-Sea) suena el teléfono; es Clement Attlee, quejándose de que alguien acaba de lanzar un pudín de bateo en él. Seagoon se encuentra con Moriarty vestido de chef y tirando de una estufa de gas portátil de la que viene el olor de budín de bateo, pero lo descarta como irrelevante para la investigación. Finalmente se descubre que el lanzador está en África, y Seagoon y Bluebottle viajan allí en un barco disfrazado de tren, hecho como un barco y pintado para aparecer como un tranvía. Después de que el barco es destruido por una mina que Eccles considera que no es un problema porque "es uno de los</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>20660</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>how long did sansar chand rule in himachal pradesh</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Khan, and regained possession of his patrimony. Sansar Chand has done a lot of work for the welfare of people mainly residing in places like Palampur, Hamirpur, Kangra. Many water distributaries were made in the name of king himself, this water was used to feed animals and for cultivation. During the campaign, Sansar Chand and his mercenary force overran other nearby principalities and compelled the submission of their rulers. He reigned over a relatively large part of present-day Himachal Pradesh for some two decades, but his ambitions brought him into conflict with the Gurkhas ruling the then nascent state of</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>¿Cuánto tiempo sansar Chand gobernó en himachal pradesh</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Jan, y recuperó la posesión de su patrimonio. Sansar Chand ha hecho mucho trabajo para el bienestar de las personas que residen principalmente en lugares como Palampur, Hamirpur, Kangra. Muchos distribuidores de agua se hicieron en nombre del propio rey, esta agua se utilizó para alimentar animales y para el cultivo. Durante la campaña, Sansar Chand y su fuerza mercenaria invadieron otros principados cercanos y obligaron a la sumisión de sus gobernantes. Reinó sobre una parte relativamente grande de la actual Himachal Pradesh durante unas dos décadas, pero sus ambiciones lo llevaron a entrar en conflicto con los Gurkhas gobernando el entonces naciente estado de</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>20661</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>what movie was the beastie boys song graffiti rock based on</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Graffiti Rock York City Breakers DJ Jimmie Jazz, Kool Moe Dee and Special K of the Treacherous Three. The New York City Breakers, who were fresh off of their success from the movie "Beat Street", made a showcase appearance. The episode also features television and film actress, Debi Mazar and actor/director Vincent Gallo (who identified as "Prince Vince") as dancers on the show. A segment of the show was sampled on The Beastie Boys' LP "Ill Communication". "[...] alright, you're scratchin it right now, cut the record back and forth against the needle, back and forth, back and forth, makin' it scratch,</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>qué película fue la canción de los chicos bestia graffiti rock basado en</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Graffiti Rock York City Breakers DJ Jimmie Jazz, Kool Moe Dee y Special K of the Treacherous Three. Los New York City Breakers, que estaban recién salidos de su éxito de la película "Beat Street", hicieron una aparición en el escaparate. El episodio también cuenta con la actriz de televisión y cine, Debi Mazar y el actor/director Vincent Gallo (quien se identificó como "Prince Vince") como bailarines en el show. Un segmento del show fue muestreado en el LP de The Beastie Boys "Ill Communication". "[...] bien, lo estás rascando ahora mismo, cortando el disco de ida y vuelta contra la aguja, de ida y vuelta, de ida y vuelta, rascándolo,</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>20662</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>who was the last person to amend the fixed index securities act</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Fixed annuity 151A claiming indexed annuities should be regulated as securities and should only be sold by registered representatives. A lawsuit was filed on the same day challenging the SEC’s ability to regulate fixed indexed annuities. Legislation was also introduced in Congress to exempt these annuities from securities regulation. On July 13, 2010, The Court of Appeals for the D.C. Circuit vacated Rule 151A. On July 21, 2010, President Obama signed HR 4173 (Dodd-Frank Wall Street Reform and Consumer Protection Act) which contained a last minute amendment by Senator Harkin (“Harkin Amendment”) which exempted fixed index annuities from regulation by the SEC</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>que fue la última persona en modificar la ley de valores de índice fijo</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>El 13 de julio de 2010, la Corte de Apelaciones del Circuito de D.C. desactivó la Regla 151A. El 21 de julio de 2010, el Presidente Obama firmó la HR 4173 (Ley de Reforma de Wall Street Dodd-Frank y Protección del Consumidor) que contenía una enmienda de última hora por el Senador Harkin (“Enmienda Harkin”) que eximía a las anualidades de índice fijo de la regulación de la SEC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>20663</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>what was the title of the debut album by the band pearl jam</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Pearl Jam 1991 United States Tour The Pearl Jam 1991 United States Tour was a concert tour by the American rock band Pearl Jam. It was the band's first tour since taking the name "Pearl Jam". The band embarked on this tour after finishing the mixing sessions for its debut album "Ten" in England. The short tour of the United States focused on the East Coast. This was the band's only tour with drummer Matt Chamberlain. Chamberlain left the band following this tour and the filming of the "Alive" video on August 3, 1991 in Seattle, Washington at RKCNDY to</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>cual fue el título del álbum debut de la banda Pearl Jam</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Pearl Jam 1991 United States Tour The Pearl Jam 1991 United States Tour fue una gira de conciertos de la banda estadounidense de rock Pearl Jam. Fue la primera gira de la banda desde que tomó el nombre de "Pearl Jam". La banda se embarcó en esta gira después de terminar las sesiones de mezcla para su álbum debut "Ten" en Inglaterra. La gira corta de los Estados Unidos se centró en la Costa Este. Esta fue la única gira de la banda con el baterista Matt Chamberlain. Chamberlain dejó la banda después de esta gira y la filmación del video "Alive" el 3 de agosto de 1991 en Seattle, Washington en RKCNDY para</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>20664</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>what is the term for a late night in montreal</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Culture of Montreal today. In part, its bustling nightlife is attributed to its relatively late "last call" (3 a.m.), a large university population, the drinking age of 18, and the excellent public transportation system combines with other aspects of the Montreal culture to make the city's night life unique. The diversity of the clubs in Montreal attests to the popularity of its night life, with night clubs, pubs, bars and singing bars ("boîte à chanson"), Latin clubs, African clubs, jazz clubs, lounges, after-hours houses, and strip clubs all attracting different types of customers. The most active parts during Montreal night life are the</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>¿cuál es el término para una noche en Montreal</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>La cultura de Montreal hoy en día. En parte, su bulliciosa vida nocturna se atribuye a su relativamente tardía "última llamada" (3 a.m.), una gran población universitaria, la edad de beber 18 años, y el excelente sistema de transporte público se combina con otros aspectos de la cultura de Montreal para hacer la vida nocturna de la ciudad única. La diversidad de los clubes en Montreal atestigua la popularidad de su vida nocturna, con clubes nocturnos, pubs, bares y bares de canto ("boîte à chanson"), clubes latinos, clubes africanos, clubs de jazz, salones, casas después de horas, y clubes de striptease que atraen a diferentes tipos de clientes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>20665</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>when did secretariat win the belmont stakes</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Kentucky Derby, Secretariat became the ninth horse to complete the Triple Crown of Thoroughbred Racing, and the first horse since Citation in 1948, ending a 25-year period without a Triple Crown winner. Secretariat's times in all three Triple Crown races were course records and still stand. In part due to accomplishing the Triple Crown and winning other races during the 1973 calendar season, Secretariat won Horse of the Year for the second consecutive year. In addition, he also won Eclipse Awards as the American Champion Three-Year-Old Male Horse and the American Champion Male Turf Horse. 1973 Belmont Stakes The 1973</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>cuando la secretaría ganó las apuestas de Belmont</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Kentucky Derby, Secretariat se convirtió en el noveno caballo en completar el Triple Crown of Thoroughbred Racing, y el primer caballo desde Citation en 1948, terminando un período de 25 años sin un ganador de Triple Crown. Los tiempos de Secretariat en las tres carreras de Triple Crown fueron récords de curso y todavía en pie. En parte debido a lograr la Triple Crown y ganar otras carreras durante la temporada de 1973, Secretariat ganó Caballo del Año por segundo año consecutivo. Además, también ganó los Premios Eclipse como el Campeón Americano de Tres Años de edad, Caballo Masculino y el Campeón Americano de Caballo Turf. 1973 Belmont Stakes The 1973</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>20666</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>what was the name of the 2003 bbc radio show in which alex parks won</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Introduction (Alex Parks album) Introduction is Alex Parks' debut album, released on 24 November 2003. Recorded and released within only two weeks of Parks winning the BBC's "Fame Academy", it included seven original compositions, mostly co-written with songwriters Helen Boulding, Gary Clark and Boo Hewerdine, as well as six cover songs from John Lennon, Tears for Fears, R.E.M., Christina Aguilera, Eurythmics and Coldplay. The album reached number 5 in the UK Top 40 Album charts. It has been classified double platinum in the UK, and gold in six other countries including Italy, Greece, Germany and Australia. "Introduction" includes rock influences</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>¿Cuál era el nombre del programa de radio de 2003 en el que Alex Parks ganó</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Introducción (Álbum de Alex Parks) Introducción es el álbum debut de Alex Parks, lanzado el 24 de noviembre de 2003. Grabado y lanzado dentro de sólo dos semanas de Parks ganando la "Fame Academy" de la BBC, incluyó siete composiciones originales, en su mayoría co-escritas con las compositoras Helen Boulding, Gary Clark y Boo Hewerdine, así como seis canciones de John Lennon, Tears for Fears, R.E.M., Christina Aguilera, Eurythmics y Coldplay. El álbum alcanzó el número 5 en el Reino Unido Top 40 Album. Ha sido clasificado doble platino en el Reino Unido, y oro en otros seis países incluyendo Italia, Grecia, Alemania y Australia. "Introducción" incluye influencias de rock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>20667</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>what region of europe was the first radio station in montenegro</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Media of Montenegro The media of Montenegro refers to mass media outlets based in Montenegro. Television, magazines, and newspapers are all operated by both state-owned and for-profit corporations which depend on advertising, subscription, and other sales-related revenues. The Constitution of Montenegro guarantees freedom of speech. As a country in transition, Montenegro's media system is under transformation. The first radio station in the Balkans and South-East Europe was established in Montenegro with the opening of a transmitter situated on the hill of Volujica near Bar by Knjaz Nikola I Petrović-Njegoš on 3 August 1904. Radio Cetinje commenced broadcasts on 27 November</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>qué región de Europa fue la primera estación de radio en Montenegro</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Medios de comunicación de Montenegro Los medios de comunicación de Montenegro se refieren a los medios de comunicación de masas con sede en Montenegro. Televisión, revistas y periódicos son operados por empresas estatales y con fines de lucro que dependen de la publicidad, la suscripción y otros ingresos relacionados con las ventas. La Constitución de Montenegro garantiza la libertad de expresión. Como país en transición, el sistema de medios de comunicación de Montenegro está en proceso de transformación. La primera estación de radio en los Balcanes y Europa sudoriental se estableció en Montenegro con la apertura de un transmisor situado en la colina de Volujica, cerca de Bar, por Knjaz Nikola I Petrović-Njegoš el 3 de agosto de 1904.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>20668</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>when did question time change to thursday night</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Question Time (TV programme) evenings. It is sometimes shown on BBC World News, depending on events in the news, and has been shown on the US channel C-SPAN. "Question Time" began on Tuesday 25 September 1979, as a television version of the BBC Radio 4 programme "Any Questions?". Originally intended to have only a short run, the programme became very popular and was duly extended. The guests on the very first show were Irish novelist Edna O'Brien, Derek Worlock; the Archbishop of Liverpool and politicians Teddy Taylor and Michael Foot. From 21 February 1980, the series moved to its current Thursday-night slot and became</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>¿Cuándo cuestionó el cambio de hora a jueves por la noche?</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>A veces se muestra en BBC World News, dependiendo de los acontecimientos en las noticias, y se ha mostrado en el canal de EE.UU. C-SPAN. "Question Time" comenzó el martes 25 de septiembre de 1979, como una versión de televisión del programa BBC Radio 4 "Any Questions?". Originalmente tenía la intención de tener sólo un corto plazo, el programa se hizo muy popular y se amplió debidamente. Los invitados en el primer show fueron la novelista irlandesa Edna O'Brien, Derek Worlock; el arzobispo de Liverpool y los políticos Teddy Taylor y Michael Foot. A partir del 21 de febrero de 1980, la serie se trasladó a su actual horario de jueves por la noche y se convirtió en</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>20669</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>the physiological significance of specific acc isozymes remains</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Acetyl-CoA carboxylase Mammalian ACC1 and ACC2 are regulated transcriptionally by multiple promoters which mediate ACC abundance in response to the cells nutritional status. Activation of gene expression through different promoters results in alternative splicing; however, the physiological significance of specific ACC isozymes remains unclear. The sensitivity to nutritional status results from the control of these promoters by transcription factors such as SREBP1c, controlled by insulin at the transcriptional level, and ChREBP, which increases in expression with high carbohydrates diets. Through a feedforward loop, citrate allosterically activates ACC. Citrate may increase ACC polymerization to increase enzymatic activity; however, it is unclear if polymerization</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>la importancia fisiológica de las isoenzimas específicas de acc permanece</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Acetil-CoA carboxilasa Mamífero ACC1 y ACC2 son regulados transcripcionalmente por múltiples promotores que median la abundancia de ACC en respuesta al estado nutricional de las células. La activación de la expresión génica a través de diferentes promotores resulta en un empalme alternativo; sin embargo, la significación fisiológica de isoenzimas ACC específicas sigue siendo poco clara. La sensibilidad al estado nutricional resulta del control de estos promotores por factores de transcripción como SREBP1c, controlado por insulina a nivel transcripcional, y ChREBP, que aumenta en expresión con dietas de alto contenido de carbohidratos. A través de un bucle de avance, citrato alostéricamente activa ACC. Citrato puede aumentar la polimerización de ACC para aumentar la actividad enzimática; sin embargo, no está claro si polimerización</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>20670</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>who is the bad boy in gud boy</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Gud Boy to impress the owner of the residence, Mihir Das (Mihir Samantray), as well as his wife, Tulasi (Priya Choudhury). He is subsequently employed as the couple's driver, having gradually won the pair over. Due to circumstance, Raja is compelled to inform Tulasi about his commitment to his dead mother and, from that point forward, Raja perceives Tulasi as a maternal figure. The film then becomes increasingly suspenseful, as a photo of Raja's mother is revealed and the audience is shown that Tulasi appears identical to the deceased woman. The narrative also explores the concept of the "good" boy or man.</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>quien es el chico malo en chico gud</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Gud Boy para impresionar al dueño de la residencia, Mihir Das (Mihir Samantray), así como a su esposa, Tulasi (Priya Choudhury). Posteriormente es empleado como conductor de la pareja, habiendo ganado gradualmente la pareja. Debido a las circunstancias, Raja se ve obligado a informar a Tulasi sobre su compromiso con su madre muerta y, desde ese punto en adelante, Raja percibe Tulasi como una figura maternal. La película se vuelve cada vez más suspensiva, ya que se revela una foto de la madre de Raja y se muestra a la audiencia que Tulasi parece idéntica a la mujer fallecida. La narración también explora el concepto del niño o hombre "bueno".</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>20671</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>where does connecticut avenue split off from dupont circle</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>shopping. As Connecticut Avenue approaches the Dupont Circle neighborhood, it splits at N Street into a through roadway and service roadways. The through roadway tunnels under Dupont Circle, while the service roadways intersect the outer roadway of the circle. Just north of the circle, the service roadways are known for their many gay-oriented businesses, of which the most famous is Lambda Rising. The through roadway and service roadways rejoin at R Street. Originally, there was no tunnel, and all vehicular traffic on Connecticut Avenue went through the circle. The tunnel was built in 1949. After crossing Florida Avenue near the</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>donde la avenida connecticut se separa del círculo dupont</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Cuando la avenida Connecticut se acerca al barrio de Dupont Circle, se divide en la calle N en un camino a través de carreteras y carreteras de servicio. Los túneles a través de carreteras bajo Dupont Circle, mientras que las carreteras de servicio cruzan la carretera exterior del círculo. Justo al norte del círculo, las carreteras de servicio son conocidas por sus muchos negocios orientados a los gays, de los cuales el más famoso es Lambda Rising. El camino a través de carreteras y carreteras de servicio se unen en la calle R. Originalmente, no había túnel, y todo el tráfico vehicular en la avenida Connecticut pasó por el círculo. El túnel fue construido en 1949.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>20672</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>lord's media centre height above ground</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Lord's Media Centre box occupied by BBC Test Match Special. The fact that the structure was built by a shipyard is betrayed by the internal doors having rounded corners similar to those in many ships. Such a door is visible in the background of the photo of the Media Centre interior. The centre stands 15 metres above the ground and its sole support comes from the structure around its two lift shafts – it is approximately the same height as the Pavilion directly opposite it on the other side of the ground. The lower tier of the centre provides accommodation for over 100</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>la altura del centro de los medios de comunicación del señor sobre el suelo</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Lord's Media Centre box ocupado por BBC Test Match Special. El hecho de que la estructura fue construida por un astillero es traicionado por las puertas internas que tienen esquinas redondeadas similares a las de muchos barcos. Tal puerta es visible en el fondo de la foto del interior de Media Centre. El centro se encuentra a 15 metros sobre el suelo y su único soporte proviene de la estructura alrededor de sus dos ejes de elevación - es aproximadamente la misma altura que el Pabellón directamente frente a él en el otro lado del suelo. El nivel inferior del centro ofrece alojamiento para más de 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>20673</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>how many players in the lorena ochoa match play</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>the Club de Golf México in Mexico City, a par-72 layout set at . In November 2016, it was announced that the event would move to the first week of May in 2017 as a match play event, the Lorena Ochoa Match Play, with a field of 64 players and $1.2 million purse. The event was not included on the 2018 schedule. During the fall of 2018, Mexican media outlets reported a possible return in time for the event to be included in the 2019 LPGA Tour season. Club de Golf México Lorena Ochoa Invitational The Lorena Ochoa Invitational was</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>cuántos jugadores en el partido de lorena ochoa juegan</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>En noviembre de 2016, se anunció que el evento se trasladaría a la primera semana de mayo de 2017 como evento de partido, el Lorena Ochoa Match Play, con un campo de 64 jugadores y monedero de 1,2 millones de dólares. El evento no se incluyó en el calendario de 2018. Durante el otoño de 2018, los medios mexicanos informaron de un posible retorno a tiempo para que el evento se incluya en la temporada 2019 del LPGA Tour. Club de Golf México Lorena Ochoa Invitacional La Lorena Ochoa Invitacional fue</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>20674</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>how much did texas a&amp;m get from the big 12</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2010–12 Southeastern Conference realignment indicated that Texas A&amp;M was torn between the Pac-10 and SEC, and was given a 72-hour deadline to decide on its future destination. Ultimately, the Texas and Oklahoma schools elected to remain in the Big 12, with A&amp;M guaranteed a $20 million annual payment from Big 12 television revenues (equal to that of Texas and Oklahoma but above that of the remaining members). Meanwhile, on the eastern side, rumored candidates included West Virginia from the Big East, and the ACC member institutions from Virginia and North Carolina excluding Wake Forest (the two "traditional Southern states" where the SEC does not</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>¿Cuánto texas a&amp;m obtuvo de los grandes 12</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>2010–12 El reajuste de la Conferencia del Sudeste indicó que Texas A&amp;M estaba dividido entre el Pac-10 y SEC, y se le dio un plazo de 72 horas para decidir su destino futuro. En última instancia, las escuelas de Texas y Oklahoma eligieron permanecer en el Big 12, con A&amp;M garantizado un pago anual de $20 millones de ingresos de la televisión Big 12 (igual a la de Texas y Oklahoma pero por encima de la de los miembros restantes). Mientras tanto, en el lado oriental, se rumoreaba que los candidatos incluían Virginia Occidental del Gran Oriente, y las instituciones miembros de ACC de Virginia y Carolina del Norte excluyendo Wake Forest (los dos "estados tradicionales del Sur" donde la SEC no</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>20675</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>what do you call a nordic skates</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Ice skate connected to the blade using a hinge. Short track racing skates have a longer overall height to the blade to allow for deep edge turns without the boot contacting the ice. For better turning ability, racing skates may have a radius, from for short track to for long track. Racing skates have a completely flat bottom. There is no hollow, only a squared off bottom with two edges. This improves glide time, by not cutting into the ice. "Touring skates" (or "Nordic skates") are long blades that can be attached, via bindings, to hiking or cross-country ski boots and are</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>¿Cómo llamas a los patines nórdicos?</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Patinaje de hielo conectado a la hoja utilizando una bisagra. Los patines de carreras cortas tienen una altura total más larga a la hoja para permitir giros de borde profundo sin que la bota se ponga en contacto con el hielo. Para una mejor capacidad de giro, los patines de carreras pueden tener un radio, desde para pista corta hasta para pista larga. Los patines de carreras tienen un fondo completamente plano. No hay hueco, sólo un fondo cuadrado con dos bordes. Esto mejora el tiempo de deslizamiento, al no cortar en el hielo. Los "patines de turismo" (o "patines nórdicos") son palas largas que se pueden unir, mediante fijaciones, a las botas de esquí de montaña o de montaña y son:</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>20676</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>what was used to seal morane's closet in the bride wore black</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>The Bride Wore Black Fergus. The five men were carelessly horsing around with a loaded rifle in an upper room across the street from the church. After the incident, they went their separate ways, intending never to reveal their involvement in the groom's death. Remorseless, Julie uses duct tape to seal the door of Morane's closet, and he suffocates to death. Julie waits in Delvaux's junkyard, planning to kill him with a handgun, but he is arrested by the police. Julie moves on to find the fifth member of the hunting group: Fergus (Charles Denner), an artist. Julie models for him as the huntress</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>lo que se usó para sellar el armario de Morane en la novia vestía negro</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Los cinco hombres estaban vagando con un rifle cargado en un cuarto superior al otro lado de la calle de la iglesia. Después del incidente, se fueron por caminos separados, con la intención de nunca revelar su participación en la muerte del novio. Sin remordimientos, Julie utiliza cinta adhesiva para sellar la puerta del armario de Morane, y se asfixia hasta la muerte. Julie espera en el depósito de chatarra de Delvaux, planeando matarlo con una pistola, pero es arrestado por la policía. Julie pasa a encontrar al quinto miembro del grupo de caza: Fergus (Charles Denner), un artista. Julie modelos para él como la cazadora</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>20677</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>what is the name of the oratorio in not the messiah</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Not the Messiah (He's a Very Naughty Boy) Not the Messiah (He's a Very Naughty Boy) is a comedic oratorio based on "Monty Python's Life of Brian". It was written by Python Eric Idle and collaborator John Du Prez, and commissioned by the Luminato festival. With the success of "Spamalot", Eric Idle's musical retelling of "Monty Python and the Holy Grail", Idle announced that he was giving "Monty Python's Life of Brian" a similar treatment. The oratorio, called "Not the Messiah", was commissioned to be part of the Luminato arts festival in June 2007. It was written and scored by</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>¿Cuál es el nombre del oratorio en no el Mesías</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>No es el Mesías (Él es un chico muy travieso) No es el Mesías (Él es un chico muy travieso) es un oratorio cómico basado en "Monty Python's Life of Brian". Fue escrito por Python Eric Idle y colaborador John Du Prez, y comisionado por el festival Luminato. Con el éxito de "Spamalot", la narración musical de Eric Idle de "Monty Python and the Holy Grial", Idle anunció que estaba dando "Monty Python's Life of Brian" un tratamiento similar. El oratorio, llamado "No el Mesías", fue comisionado para ser parte del festival de artes Luminato en junio de 2007.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
